--- a/public/templates/store-import-template.xlsx
+++ b/public/templates/store-import-template.xlsx
@@ -3,11 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Stores" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!#REF!</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -400,20 +397,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:O3"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="15.83203125" customWidth="1"/>
     <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="40.83203125" customWidth="1"/>
-    <col min="12" max="12" width="40.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="40.83203125" customWidth="1"/>
+    <col min="15" max="15" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -427,30 +427,39 @@
         <v>City</v>
       </c>
       <c r="D1" t="str">
+        <v>Full Address</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Latitude</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Longitude</v>
+      </c>
+      <c r="G1" t="str">
         <v>partneraBrandIds</v>
       </c>
-      <c r="E1" t="str">
+      <c r="H1" t="str">
         <v>partnerBrandTypes</v>
       </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>Store Category</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>Store Channel</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>City Tier</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>State</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>Priority</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>Executive_IDs</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>POC's Name</v>
       </c>
     </row>
@@ -465,31 +474,40 @@
         <v>Greater Noida</v>
       </c>
       <c r="D2" t="str">
+        <v>Plot No. 1, Commercial Belt, Alpha 1, Greater Noida, UP</v>
+      </c>
+      <c r="E2">
+        <v>28.4682</v>
+      </c>
+      <c r="F2">
+        <v>77.5115</v>
+      </c>
+      <c r="G2" t="str">
         <v>brand_002</v>
       </c>
-      <c r="E2" t="str">
+      <c r="H2" t="str">
         <v>A+</v>
       </c>
-      <c r="F2" t="str">
+      <c r="I2" t="str">
         <v>LFR</v>
       </c>
-      <c r="G2" t="str">
+      <c r="J2" t="str">
         <v>Offline</v>
       </c>
-      <c r="H2" t="str">
+      <c r="K2" t="str">
         <v>Tier 1</v>
       </c>
-      <c r="I2" t="str">
+      <c r="L2" t="str">
         <v>Uttar Pradesh</v>
       </c>
-      <c r="J2" t="str">
+      <c r="M2" t="str">
         <v>p1</v>
       </c>
-      <c r="K2" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
+      <c r="N2" t="str">
+        <v>executive_00002, executive_00003</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Kanishk Bhardwaj, Vikash Dubey</v>
       </c>
     </row>
     <row r="3">
@@ -497,308 +515,51 @@
         <v>store_000002</v>
       </c>
       <c r="B3" t="str">
-        <v>VS-VIJAY SALES (SEC 18)</v>
+        <v>CROMA (NOIDA SECTOR 18)</v>
       </c>
       <c r="C3" t="str">
         <v>Noida</v>
       </c>
       <c r="D3" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E3" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F3" t="str">
+        <v>G-54, Sector 18, Noida, UP</v>
+      </c>
+      <c r="E3">
+        <v>28.5708</v>
+      </c>
+      <c r="F3">
+        <v>77.3261</v>
+      </c>
+      <c r="G3" t="str">
+        <v>brand_001, brand_003</v>
+      </c>
+      <c r="H3" t="str">
+        <v>A, B</v>
+      </c>
+      <c r="I3" t="str">
         <v>LFR</v>
       </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
         <v>Offline</v>
       </c>
-      <c r="H3" t="str">
+      <c r="K3" t="str">
         <v>Tier 1</v>
       </c>
-      <c r="I3" t="str">
+      <c r="L3" t="str">
         <v>Uttar Pradesh</v>
       </c>
-      <c r="J3" t="str">
+      <c r="M3" t="str">
         <v>p2</v>
       </c>
-      <c r="K3" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>store_000003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>VS-VIJAY SALES (RDC)</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Ghaziabad</v>
-      </c>
-      <c r="D4" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F4" t="str">
-        <v>LFR</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Offline</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Uttar Pradesh</v>
-      </c>
-      <c r="J4" t="str">
-        <v>p3</v>
-      </c>
-      <c r="K4" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>store_000004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>VS-VIJAY SALES (GOUR CHOWK)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Greater Noida</v>
-      </c>
-      <c r="D5" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E5" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F5" t="str">
-        <v>LFR</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Offline</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Uttar Pradesh</v>
-      </c>
-      <c r="J5" t="str">
-        <v>p1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>store_000005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VS-VIJAY SALES (INDRAPURAM)</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Ghaziabad</v>
-      </c>
-      <c r="D6" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E6" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F6" t="str">
-        <v>LFR</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Offline</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Uttar Pradesh</v>
-      </c>
-      <c r="J6" t="str">
-        <v>p2</v>
-      </c>
-      <c r="K6" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>store_000006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Croma-Agra-SRK Mall</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Agra</v>
-      </c>
-      <c r="D7" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E7" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F7" t="str">
-        <v>LFR</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Offline</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Uttar Pradesh</v>
-      </c>
-      <c r="J7" t="str">
-        <v>p3</v>
-      </c>
-      <c r="K7" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>store_000007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Croma-Bulandshahr-Raja Babu Road</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Bulandshahr</v>
-      </c>
-      <c r="D8" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E8" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F8" t="str">
-        <v>LFR</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Offline</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Uttar Pradesh</v>
-      </c>
-      <c r="J8" t="str">
-        <v>p1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>store_000008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Croma-Agra-Fatehabad Road</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Agra</v>
-      </c>
-      <c r="D9" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E9" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F9" t="str">
-        <v>LFR</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Offline</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Uttar Pradesh</v>
-      </c>
-      <c r="J9" t="str">
-        <v>p2</v>
-      </c>
-      <c r="K9" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>store_000009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Croma-Agra-Church Road</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Agra</v>
-      </c>
-      <c r="D10" t="str">
-        <v>brand_002</v>
-      </c>
-      <c r="E10" t="str">
-        <v>A+</v>
-      </c>
-      <c r="F10" t="str">
-        <v>LFR</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Offline</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Uttar Pradesh</v>
-      </c>
-      <c r="J10" t="str">
-        <v>p3</v>
-      </c>
-      <c r="K10" t="str">
-        <v>executive_00002 ,executive_00003 , executive_00008</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Kanishk Bhardwaj ,Vikash Dubey , Gautam</v>
+      <c r="N3" t="str">
+        <v>executive_00008</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Gautam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
   </ignoredErrors>
 </worksheet>
 </file>